--- a/output/quickfixopen1_portfolio_daily.xlsx
+++ b/output/quickfixopen1_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$185</f>
+              <f>'equity_curve'!$A$2:$A$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$185</f>
+              <f>'equity_curve'!$B$2:$B$186</f>
             </numRef>
           </val>
         </ser>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-30</t>
+          <t>2025-12-18 -&gt; 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5477,6 +5477,26 @@
           <t>NY_Natural_Gas_Futures exit_open (+6,605)</t>
         </is>
       </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>429767.74</v>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>429767.74</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/quickfixopen1_portfolio_daily.xlsx
+++ b/output/quickfixopen1_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>42% of trading days</t>
+          <t>41% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5497,6 +5497,46 @@
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>429767.74</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>429767.74</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>429767.74</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>429767.74</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/quickfixopen1_portfolio_daily.xlsx
+++ b/output/quickfixopen1_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>429,767.74</t>
+          <t>441,364.12</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+329.77%</t>
+          <t>+341.36%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>441,128  (+341.13%)</t>
+          <t>453,071  (+353.07%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,949  (11.4 pts of return)</t>
+          <t>5,988  (11.7 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>78.4x</t>
+          <t>81.2x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>88.4%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+1.97R  (best +8.92R)</t>
+          <t>+1.93R  (best +8.92R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4,214  (+1.97%)</t>
+          <t>4,202  (+1.93%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5538,6 +5538,62 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
     </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>429767.74</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>12764.53</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>417003.21</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 4,298); Nasdaq_100_E_mini short (risk 4,255); S_P_500_E_mini short (risk 4,212)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>441364.12</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>441364.12</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 4,170)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini exit_open (+7,590); NY_Platinum_Futures exit_open (+2,567); S_P_500_E_mini exit_open (+1,446)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5550,7 +5606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5562,7 +5618,7 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
@@ -10327,6 +10383,202 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>736432.47</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>10236.41</v>
+      </c>
+      <c r="K94" s="6" t="n">
+        <v>6113.75</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>760537.26</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1.784</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1.784</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>726196.0600000001</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>10094.13</v>
+      </c>
+      <c r="K95" s="6" t="n">
+        <v>18007.81</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>754423.51</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>716101.9399999999</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>9953.82</v>
+      </c>
+      <c r="K96" s="6" t="n">
+        <v>3417.91</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>763955.17</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>706148.12</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>9815.459999999999</v>
+      </c>
+      <c r="K97" s="7" t="n">
+        <v>-16.78</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>736415.7</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/quickfixopen1_portfolio_daily.xlsx
+++ b/output/quickfixopen1_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>441,364.12</t>
+          <t>441,811.31</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+341.36%</t>
+          <t>+341.81%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>453,071  (+353.07%)</t>
+          <t>453,583  (+353.58%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,988  (11.7 pts of return)</t>
+          <t>6,040  (11.8 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>81.2x</t>
+          <t>81.3x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>88.5%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+1.93R  (best +8.92R)</t>
+          <t>+1.91R  (best +8.92R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4,202  (+1.93%)</t>
+          <t>4,158  (+1.91%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>41% of trading days</t>
+          <t>42% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5571,26 +5571,58 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>441364.12</v>
+        <v>441371.25</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>4170.03</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>437201.22</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 4,170)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini exit_open (+7,590); NY_Platinum_Futures exit_open (+2,567); S_P_500_E_mini exit_open (+1,446)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>441811.31</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>441364.12</v>
-      </c>
-      <c r="E190" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 4,170)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini exit_open (+7,590); NY_Platinum_Futures exit_open (+2,567); S_P_500_E_mini exit_open (+1,446)</t>
+      <c r="D191" s="5" t="n">
+        <v>441811.31</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 4,372); NY_Palladium_Futures short (risk 4,328); NY_Platinum_Futures short (risk 4,285)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX exit_open (+485); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10426,7 +10458,7 @@
         <v>6113.75</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>760537.26</v>
+        <v>760554.04</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -10477,7 +10509,7 @@
         <v>18007.81</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>754423.51</v>
+        <v>754440.29</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -10528,7 +10560,7 @@
         <v>3417.91</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>763955.17</v>
+        <v>763971.95</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -10552,14 +10584,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="G97" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.002</v>
+        <v>0.116</v>
       </c>
       <c r="I97" s="5" t="n">
         <v>706148.12</v>
@@ -10567,13 +10607,142 @@
       <c r="J97" s="5" t="n">
         <v>9815.459999999999</v>
       </c>
-      <c r="K97" s="7" t="n">
-        <v>-16.78</v>
+      <c r="K97" s="6" t="n">
+        <v>1141.35</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>736415.7</v>
+        <v>765113.3100000001</v>
       </c>
       <c r="M97" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H98" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>754156.49</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>10482.78</v>
+      </c>
+      <c r="K98" s="7" t="n">
+        <v>-28.33</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>765084.97</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>743673.72</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>10337.06</v>
+      </c>
+      <c r="K99" s="7" t="n">
+        <v>-40.54</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>765044.4399999999</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>733336.65</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>10193.38</v>
+      </c>
+      <c r="K100" s="7" t="n">
+        <v>-38.18</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>765006.26</v>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
